--- a/output/pdf_financials_xlsx/GUF.xlsx
+++ b/output/pdf_financials_xlsx/GUF.xlsx
@@ -2108,31 +2108,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.330103</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.173469</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.119377</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.180217</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.108709</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.355638</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.283625</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.147875</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.178058</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.185227</v>
@@ -2144,7 +2144,7 @@
         <v>0.35681</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.044168</v>
       </c>
     </row>
     <row r="35">
@@ -2200,31 +2200,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.330103</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.173469</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.119377</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.180217</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.108709</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.355638</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.283625</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.147875</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.178058</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.185227</v>
@@ -2236,7 +2236,7 @@
         <v>0.35681</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.044168</v>
       </c>
     </row>
     <row r="37">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
